--- a/output/processing/124-125_844_C.xlsx
+++ b/output/processing/124-125_844_C.xlsx
@@ -535,18 +535,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -653,11 +653,57 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>altO</t>
-        </is>
-      </c>
+          <t>844 C Z16</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>220-240V~ 50/60 Hz</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>230 W</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IP44</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-20° ÷ +55°C *</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Uso continuo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9.6 m/min</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>18 µF</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
